--- a/ch_04_eda/ch_04.xlsx
+++ b/ch_04_eda/ch_04.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\python-in-excel-book-staging\new_datasets\ch_04_eda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_04_eda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9652A154-F78F-43A7-B91F-F16E0266141E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A488D8B6-8492-4A17-BD5B-7009DD4C8EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1039,7 +1039,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7D35ED8-82FD-4F2C-AC14-355402958DA6}" name="mpg_2" displayName="mpg_2" ref="A1:I399" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7D35ED8-82FD-4F2C-AC14-355402958DA6}" name="mpg" displayName="mpg" ref="A1:I399" totalsRowShown="0">
   <autoFilter ref="A1:I399" xr:uid="{E7D35ED8-82FD-4F2C-AC14-355402958DA6}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{44C9E329-1563-4922-A53D-1B0DE7743033}" name="mpg"/>
@@ -1342,19 +1342,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I399"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.1171875" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12.41015625" customWidth="1"/>
-    <col min="5" max="5" width="8.1171875" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="5" max="5" width="8.1328125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.234375" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>18</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>15</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>18</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>16</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>17</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>15</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>14</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>14</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>14</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>15</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>15</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>14</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>15</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>24</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>22</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>18</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>21</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>27</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>26</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>25</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>24</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>25</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>26</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>21</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>10</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>10</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>11</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>9</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>25</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>25</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>19</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>16</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>17</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>19</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>18</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>14</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>14</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>14</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>14</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>12</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>13</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>13</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>18</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>22</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>19</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>18</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>23</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>28</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>30</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>30</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>31</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>35</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>27</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>26</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>24</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>25</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>23</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>20</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>21</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>13</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>14</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>15</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>14</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>17</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>11</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>13</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>12</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>13</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>19</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>15</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>13</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>13</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>14</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>18</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>22</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>21</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>26</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>22</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>28</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>23</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>28</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>27</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>13</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>14</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>13</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>14</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>15</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>12</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>13</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>13</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>14</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>13</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>13</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>18</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>16</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>18</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>18</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>23</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>26</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>11</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>12</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>13</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>12</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>18</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>20</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>21</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>22</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>18</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>19</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>21</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>26</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>15</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>16</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>29</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>24</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>20</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>19</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>15</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>24</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>20</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>11</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>20</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>21</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>19</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>15</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>31</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>26</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>32</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>25</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>16</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>16</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>18</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>16</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>13</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>14</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>14</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>14</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>29</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>26</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>26</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>31</v>
       </c>
@@ -5582,7 +5582,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>32</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>28</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>24</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>26</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>24</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>26</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>31</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>19</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>18</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>15</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>15</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>16</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>15</v>
       </c>
@@ -5959,7 +5959,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>16</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>14</v>
       </c>
@@ -6017,7 +6017,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>17</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>16</v>
       </c>
@@ -6075,7 +6075,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>15</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>18</v>
       </c>
@@ -6133,7 +6133,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>21</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>20</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>13</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>29</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>23</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>20</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>23</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>24</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>25</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>24</v>
       </c>
@@ -6423,7 +6423,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>18</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>29</v>
       </c>
@@ -6481,7 +6481,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>19</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>23</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>23</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>22</v>
       </c>
@@ -6597,7 +6597,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>25</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>33</v>
       </c>
@@ -6655,7 +6655,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>28</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>25</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>25</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>26</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>27</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>17.5</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>16</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>15.5</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>14.5</v>
       </c>
@@ -6916,7 +6916,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>22</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>22</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>24</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>22.5</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>29</v>
       </c>
@@ -7061,7 +7061,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>24.5</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>29</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>33</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>20</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>18</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>18.5</v>
       </c>
@@ -7235,7 +7235,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>17.5</v>
       </c>
@@ -7264,7 +7264,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>29.5</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>32</v>
       </c>
@@ -7322,7 +7322,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>28</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>26.5</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>20</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>13</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>19</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>19</v>
       </c>
@@ -7496,7 +7496,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>16.5</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>16.5</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>13</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>13</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>13</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>31.5</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>30</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>36</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>25.5</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>33.5</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>17.5</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>17</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>15.5</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>15</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>17.5</v>
       </c>
@@ -7931,7 +7931,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>20.5</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>19</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>18.5</v>
       </c>
@@ -8018,7 +8018,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>16</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>15.5</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>15.5</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>16</v>
       </c>
@@ -8134,7 +8134,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>29</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>24.5</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>26</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>25.5</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>30.5</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>33.5</v>
       </c>
@@ -8308,7 +8308,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>30</v>
       </c>
@@ -8337,7 +8337,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>30.5</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>22</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>21.5</v>
       </c>
@@ -8424,7 +8424,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>21.5</v>
       </c>
@@ -8453,7 +8453,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>43.1</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>36.1</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>32.799999999999997</v>
       </c>
@@ -8540,7 +8540,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>39.4</v>
       </c>
@@ -8569,7 +8569,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>36.1</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>19.899999999999999</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>19.399999999999999</v>
       </c>
@@ -8656,7 +8656,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>20.2</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>19.2</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>20.5</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>20.2</v>
       </c>
@@ -8772,7 +8772,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>25.1</v>
       </c>
@@ -8801,7 +8801,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>20.5</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>19.399999999999999</v>
       </c>
@@ -8859,7 +8859,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>20.6</v>
       </c>
@@ -8888,7 +8888,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>20.8</v>
       </c>
@@ -8917,7 +8917,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>18.600000000000001</v>
       </c>
@@ -8946,7 +8946,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>18.100000000000001</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>19.2</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>17.7</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>18.100000000000001</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>17.5</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>30</v>
       </c>
@@ -9120,7 +9120,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>27.5</v>
       </c>
@@ -9149,7 +9149,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>27.2</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>30.9</v>
       </c>
@@ -9207,7 +9207,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>21.1</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>23.2</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>23.8</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>23.9</v>
       </c>
@@ -9323,7 +9323,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>20.3</v>
       </c>
@@ -9352,7 +9352,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>17</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>21.6</v>
       </c>
@@ -9410,7 +9410,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>16.2</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>31.5</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>29.5</v>
       </c>
@@ -9497,7 +9497,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>21.5</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>19.8</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>22.3</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>20.2</v>
       </c>
@@ -9613,7 +9613,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>20.6</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>17</v>
       </c>
@@ -9671,7 +9671,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>17.600000000000001</v>
       </c>
@@ -9700,7 +9700,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>16.5</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>18.2</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>16.899999999999999</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>15.5</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>19.2</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>18.5</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>31.9</v>
       </c>
@@ -9903,7 +9903,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>34.1</v>
       </c>
@@ -9932,7 +9932,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>35.700000000000003</v>
       </c>
@@ -9961,7 +9961,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>27.4</v>
       </c>
@@ -9990,7 +9990,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>25.4</v>
       </c>
@@ -10019,7 +10019,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>23</v>
       </c>
@@ -10048,7 +10048,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>27.2</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>23.9</v>
       </c>
@@ -10106,7 +10106,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>34.200000000000003</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>34.5</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>31.8</v>
       </c>
@@ -10193,7 +10193,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>37.299999999999997</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>28.4</v>
       </c>
@@ -10251,7 +10251,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>28.8</v>
       </c>
@@ -10280,7 +10280,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>26.8</v>
       </c>
@@ -10309,7 +10309,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>33.5</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>41.5</v>
       </c>
@@ -10367,7 +10367,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>38.1</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>32.1</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>37.200000000000003</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>28</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>26.4</v>
       </c>
@@ -10512,7 +10512,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>24.3</v>
       </c>
@@ -10541,7 +10541,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>19.100000000000001</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>34.299999999999997</v>
       </c>
@@ -10599,7 +10599,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>29.8</v>
       </c>
@@ -10628,7 +10628,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>31.3</v>
       </c>
@@ -10657,7 +10657,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>37</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>32.200000000000003</v>
       </c>
@@ -10715,7 +10715,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>46.6</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>27.9</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>40.799999999999997</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>44.3</v>
       </c>
@@ -10831,7 +10831,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>43.4</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>36.4</v>
       </c>
@@ -10889,7 +10889,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>30</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>44.6</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>40.9</v>
       </c>
@@ -10973,7 +10973,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>33.799999999999997</v>
       </c>
@@ -11002,7 +11002,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>29.8</v>
       </c>
@@ -11031,7 +11031,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>32.700000000000003</v>
       </c>
@@ -11060,7 +11060,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>23.7</v>
       </c>
@@ -11089,7 +11089,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>35</v>
       </c>
@@ -11118,7 +11118,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>23.6</v>
       </c>
@@ -11144,7 +11144,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>32.4</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>27.2</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>26.6</v>
       </c>
@@ -11231,7 +11231,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>25.8</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>23.5</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>30</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>39.1</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>39</v>
       </c>
@@ -11376,7 +11376,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>35.1</v>
       </c>
@@ -11405,7 +11405,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>32.299999999999997</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>37</v>
       </c>
@@ -11463,7 +11463,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>37.700000000000003</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>34.1</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>34.700000000000003</v>
       </c>
@@ -11550,7 +11550,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>34.4</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>29.9</v>
       </c>
@@ -11608,7 +11608,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>33</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>34.5</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>33.700000000000003</v>
       </c>
@@ -11692,7 +11692,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>32.4</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>32.9</v>
       </c>
@@ -11750,7 +11750,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>31.6</v>
       </c>
@@ -11779,7 +11779,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>28.1</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>30.7</v>
       </c>
@@ -11837,7 +11837,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>25.4</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>24.2</v>
       </c>
@@ -11895,7 +11895,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>22.4</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>26.6</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>20.2</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>17.600000000000001</v>
       </c>
@@ -12011,7 +12011,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>28</v>
       </c>
@@ -12040,7 +12040,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>27</v>
       </c>
@@ -12069,7 +12069,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>34</v>
       </c>
@@ -12098,7 +12098,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>31</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>29</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>27</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>24</v>
       </c>
@@ -12214,7 +12214,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>23</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>36</v>
       </c>
@@ -12269,7 +12269,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>37</v>
       </c>
@@ -12298,7 +12298,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>31</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>38</v>
       </c>
@@ -12356,7 +12356,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>36</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>36</v>
       </c>
@@ -12414,7 +12414,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>36</v>
       </c>
@@ -12443,7 +12443,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>34</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>38</v>
       </c>
@@ -12501,7 +12501,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>32</v>
       </c>
@@ -12530,7 +12530,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>38</v>
       </c>
@@ -12559,7 +12559,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>25</v>
       </c>
@@ -12588,7 +12588,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>38</v>
       </c>
@@ -12617,7 +12617,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>26</v>
       </c>
@@ -12646,7 +12646,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>22</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>32</v>
       </c>
@@ -12704,7 +12704,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>36</v>
       </c>
@@ -12733,7 +12733,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>27</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>27</v>
       </c>
@@ -12791,7 +12791,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>44</v>
       </c>
@@ -12820,7 +12820,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>32</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>28</v>
       </c>
@@ -12878,7 +12878,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>31</v>
       </c>
